--- a/backend/data/SAP Item Master 24.xlsx
+++ b/backend/data/SAP Item Master 24.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://akshayakalpafarmsandfoods-my.sharepoint.com/personal/srinivasulu_balram_akshayakalpa_org/Documents/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="485" documentId="8_{E58D2A99-F11F-4979-AE4E-3BBAEDA44966}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{01662C37-5916-456E-8AD3-19E1E220FA94}"/>
+  <xr:revisionPtr revIDLastSave="515" documentId="8_{E58D2A99-F11F-4979-AE4E-3BBAEDA44966}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{522AE41C-D832-4B1A-A4E3-6EAC4B909607}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{CA1195A1-03B4-439D-A5A3-292FF1755D3F}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$O$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$O$22</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="150">
   <si>
     <t>Product</t>
   </si>
@@ -48,9 +48,6 @@
     <t>Product Description</t>
   </si>
   <si>
-    <t>Product Type</t>
-  </si>
-  <si>
     <t>Division</t>
   </si>
   <si>
@@ -141,9 +138,6 @@
     <t>1200000027</t>
   </si>
   <si>
-    <t>Organic Cow Ghee 5Ltr</t>
-  </si>
-  <si>
     <t>Organic Cow Ghee-5 ltr</t>
   </si>
   <si>
@@ -159,9 +153,6 @@
     <t>1200000029</t>
   </si>
   <si>
-    <t>Organic Desi Cow Ghee 5Ltr</t>
-  </si>
-  <si>
     <t>Organic Desi Cow Ghee-5 ltr</t>
   </si>
   <si>
@@ -453,9 +444,6 @@
     <t>AK Organic Desi Cow Ghee- 1000 ml</t>
   </si>
   <si>
-    <t>Organic Cow Ghee 490ml</t>
-  </si>
-  <si>
     <t>1300000028</t>
   </si>
   <si>
@@ -472,6 +460,36 @@
   </si>
   <si>
     <t>AK Virgin Coconut Oil, 500ml</t>
+  </si>
+  <si>
+    <t>zzz</t>
+  </si>
+  <si>
+    <t>1200000068</t>
+  </si>
+  <si>
+    <t>Organic Cow Ghee 1000 ml</t>
+  </si>
+  <si>
+    <t>Organic Cow Ghee-1 ltr</t>
+  </si>
+  <si>
+    <t>AKGHCG1L</t>
+  </si>
+  <si>
+    <t>Akshayakalpa Organic Cow Ghee - 1000ml</t>
+  </si>
+  <si>
+    <t>AK Organic Cow Ghee - 1000 ml</t>
+  </si>
+  <si>
+    <t>Organic Cow Ghee 490 ml</t>
+  </si>
+  <si>
+    <t>Organic Cow Ghee 5 Ltr</t>
+  </si>
+  <si>
+    <t>Organic Desi Cow Ghee 5 Ltr</t>
   </si>
 </sst>
 </file>
@@ -902,75 +920,75 @@
         <v>1</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="M1" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="N1" s="1" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B2">
         <v>1200000002</v>
       </c>
       <c r="C2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" t="s">
         <v>15</v>
-      </c>
-      <c r="D2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F2" t="s">
-        <v>16</v>
       </c>
       <c r="G2" s="3">
         <v>0.05</v>
       </c>
       <c r="H2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I2" t="s">
         <v>17</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>18</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
         <v>19</v>
-      </c>
-      <c r="K2" t="s">
-        <v>20</v>
       </c>
       <c r="L2">
         <v>69</v>
@@ -979,45 +997,45 @@
         <v>756</v>
       </c>
       <c r="N2" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="O2" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B3">
         <v>1200000011</v>
       </c>
       <c r="C3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="2" t="s">
-        <v>13</v>
-      </c>
       <c r="F3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G3" s="3">
         <v>0.05</v>
       </c>
       <c r="H3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I3" t="s">
         <v>23</v>
       </c>
-      <c r="I3" t="s">
+      <c r="J3" t="s">
         <v>24</v>
       </c>
-      <c r="J3" t="s">
+      <c r="K3" t="s">
         <v>25</v>
-      </c>
-      <c r="K3" t="s">
-        <v>26</v>
       </c>
       <c r="L3">
         <v>68</v>
@@ -1026,45 +1044,45 @@
         <v>362</v>
       </c>
       <c r="N3" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="O3" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B4">
         <v>1200000012</v>
       </c>
       <c r="C4" t="s">
-        <v>137</v>
+        <v>147</v>
       </c>
       <c r="D4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E4" s="2" t="s">
-        <v>13</v>
-      </c>
       <c r="F4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G4" s="3">
         <v>0.05</v>
       </c>
       <c r="H4" t="s">
+        <v>27</v>
+      </c>
+      <c r="I4" t="s">
         <v>28</v>
       </c>
-      <c r="I4" t="s">
+      <c r="J4" t="s">
         <v>29</v>
       </c>
-      <c r="J4" t="s">
+      <c r="K4" t="s">
         <v>30</v>
-      </c>
-      <c r="K4" t="s">
-        <v>31</v>
       </c>
       <c r="L4">
         <v>67</v>
@@ -1073,832 +1091,832 @@
         <v>876</v>
       </c>
       <c r="N4" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="O4" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>32</v>
+        <v>141</v>
       </c>
       <c r="B5">
-        <v>1200000027</v>
+        <v>1200000068</v>
       </c>
       <c r="C5" t="s">
-        <v>33</v>
+        <v>142</v>
       </c>
       <c r="D5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="2" t="s">
-        <v>13</v>
-      </c>
       <c r="F5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G5" s="3">
         <v>0.05</v>
       </c>
       <c r="H5" t="s">
-        <v>34</v>
+        <v>143</v>
       </c>
       <c r="I5" t="s">
-        <v>35</v>
+        <v>144</v>
       </c>
       <c r="J5" t="s">
-        <v>36</v>
+        <v>145</v>
       </c>
       <c r="K5" t="s">
-        <v>37</v>
+        <v>146</v>
       </c>
       <c r="L5">
-        <v>71</v>
+        <v>119</v>
       </c>
       <c r="M5">
-        <v>8706</v>
+        <v>1752</v>
       </c>
       <c r="N5" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="O5" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>38</v>
+        <v>77</v>
       </c>
       <c r="B6">
-        <v>1200000029</v>
+        <v>1200000069</v>
       </c>
       <c r="C6" t="s">
-        <v>39</v>
+        <v>78</v>
       </c>
       <c r="D6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E6" s="2" t="s">
-        <v>13</v>
-      </c>
       <c r="F6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G6" s="3">
         <v>0.05</v>
       </c>
       <c r="H6" t="s">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="I6" t="s">
-        <v>41</v>
+        <v>80</v>
       </c>
       <c r="J6" t="s">
-        <v>42</v>
+        <v>81</v>
       </c>
       <c r="K6" t="s">
-        <v>43</v>
+        <v>133</v>
       </c>
       <c r="L6">
-        <v>73</v>
+        <v>120</v>
       </c>
       <c r="M6">
-        <v>12539</v>
+        <v>2509</v>
       </c>
       <c r="N6" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="O6" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="B7">
-        <v>1200000038</v>
+        <v>1200000027</v>
       </c>
       <c r="C7" t="s">
-        <v>45</v>
+        <v>148</v>
       </c>
       <c r="D7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E7" s="2" t="s">
-        <v>13</v>
-      </c>
       <c r="F7" t="s">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="G7" s="3">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="H7" t="s">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="I7" t="s">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="J7" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="K7" t="s">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="L7">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="M7">
-        <v>126</v>
+        <v>8706</v>
       </c>
       <c r="N7" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="O7" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>51</v>
+        <v>36</v>
       </c>
       <c r="B8">
-        <v>1200000039</v>
+        <v>1200000029</v>
       </c>
       <c r="C8" t="s">
-        <v>52</v>
+        <v>149</v>
       </c>
       <c r="D8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E8" s="2" t="s">
-        <v>13</v>
-      </c>
       <c r="F8" t="s">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="G8" s="3">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="H8" t="s">
-        <v>53</v>
+        <v>37</v>
       </c>
       <c r="I8" t="s">
-        <v>54</v>
+        <v>38</v>
       </c>
       <c r="J8" t="s">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="K8" t="s">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c r="L8">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="M8">
-        <v>36</v>
+        <v>12539</v>
       </c>
       <c r="N8" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="O8" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>57</v>
+        <v>41</v>
       </c>
       <c r="B9">
-        <v>1200000040</v>
+        <v>1200000038</v>
       </c>
       <c r="C9" t="s">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="D9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E9" s="2" t="s">
-        <v>13</v>
-      </c>
       <c r="F9" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="G9" s="3">
         <v>0</v>
       </c>
       <c r="H9" t="s">
-        <v>59</v>
+        <v>44</v>
       </c>
       <c r="I9" t="s">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="J9" t="s">
-        <v>61</v>
+        <v>46</v>
       </c>
       <c r="K9" t="s">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="L9">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="M9">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="N9" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="O9" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="B10">
-        <v>1200000041</v>
+        <v>1200000040</v>
       </c>
       <c r="C10" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="D10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E10" s="2" t="s">
-        <v>13</v>
-      </c>
       <c r="F10" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="G10" s="3">
         <v>0</v>
       </c>
       <c r="H10" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="I10" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="J10" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="K10" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="L10">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="M10">
-        <v>31</v>
+        <v>136</v>
       </c>
       <c r="N10" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="O10" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>80</v>
+        <v>48</v>
       </c>
       <c r="B11">
-        <v>1200000069</v>
+        <v>1200000039</v>
       </c>
       <c r="C11" t="s">
-        <v>81</v>
+        <v>49</v>
       </c>
       <c r="D11" t="s">
+        <v>11</v>
+      </c>
+      <c r="E11" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E11" s="2" t="s">
-        <v>13</v>
-      </c>
       <c r="F11" t="s">
-        <v>16</v>
+        <v>43</v>
       </c>
       <c r="G11" s="3">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="H11" t="s">
-        <v>82</v>
+        <v>50</v>
       </c>
       <c r="I11" t="s">
-        <v>83</v>
+        <v>51</v>
       </c>
       <c r="J11" t="s">
-        <v>84</v>
+        <v>52</v>
       </c>
       <c r="K11" t="s">
-        <v>136</v>
+        <v>53</v>
       </c>
       <c r="L11">
-        <v>120</v>
+        <v>77</v>
       </c>
       <c r="M11">
-        <v>2509</v>
+        <v>36</v>
       </c>
       <c r="N11" t="s">
+        <v>126</v>
+      </c>
+      <c r="O11" t="s">
         <v>128</v>
       </c>
-      <c r="O11" t="s">
-        <v>130</v>
-      </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A12" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="B12" s="4">
-        <v>1300000048</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="E12" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="F12" s="4" t="s">
-        <v>90</v>
+      <c r="A12" t="s">
+        <v>60</v>
+      </c>
+      <c r="B12">
+        <v>1200000041</v>
+      </c>
+      <c r="C12" t="s">
+        <v>61</v>
+      </c>
+      <c r="D12" t="s">
+        <v>11</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F12" t="s">
+        <v>43</v>
       </c>
       <c r="G12" s="3">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="H12" t="s">
-        <v>91</v>
+        <v>62</v>
       </c>
       <c r="I12" t="s">
-        <v>92</v>
+        <v>63</v>
       </c>
       <c r="J12" t="s">
-        <v>93</v>
+        <v>64</v>
       </c>
       <c r="K12" t="s">
-        <v>91</v>
+        <v>65</v>
       </c>
       <c r="L12">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="M12">
-        <v>899</v>
+        <v>31</v>
       </c>
       <c r="N12" t="s">
+        <v>126</v>
+      </c>
+      <c r="O12" t="s">
         <v>128</v>
-      </c>
-      <c r="O12" t="s">
-        <v>130</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A13" s="4" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="B13" s="4">
-        <v>1300000089</v>
+        <v>1300000048</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="G13" s="3">
         <v>0.05</v>
       </c>
       <c r="H13" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="I13" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="J13" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="K13" t="s">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="L13">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="M13">
-        <v>425</v>
+        <v>899</v>
       </c>
       <c r="N13" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="O13" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A14" s="4" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="B14" s="4">
-        <v>1300000090</v>
+        <v>1300000089</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="G14" s="3">
         <v>0.05</v>
       </c>
       <c r="H14" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="I14" t="s">
-        <v>104</v>
+        <v>95</v>
       </c>
       <c r="J14" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="K14" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="L14">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="M14">
-        <v>525</v>
+        <v>425</v>
       </c>
       <c r="N14" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="O14" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A15" s="4" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="B15" s="4">
-        <v>1300000091</v>
+        <v>1300000090</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="G15" s="3">
         <v>0.05</v>
       </c>
       <c r="H15" t="s">
-        <v>109</v>
+        <v>100</v>
       </c>
       <c r="I15" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="J15" t="s">
-        <v>111</v>
+        <v>102</v>
       </c>
       <c r="K15" t="s">
-        <v>112</v>
+        <v>103</v>
       </c>
       <c r="L15">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="M15">
-        <v>440</v>
+        <v>525</v>
       </c>
       <c r="N15" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="O15" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A16" s="4" t="s">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="B16" s="4">
-        <v>1300000092</v>
+        <v>1300000091</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="G16" s="3">
         <v>0.05</v>
       </c>
       <c r="H16" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="I16" t="s">
-        <v>116</v>
+        <v>107</v>
       </c>
       <c r="J16" t="s">
-        <v>117</v>
+        <v>108</v>
+      </c>
+      <c r="K16" t="s">
+        <v>109</v>
+      </c>
+      <c r="L16">
+        <v>103</v>
       </c>
       <c r="M16">
-        <v>4395</v>
+        <v>440</v>
       </c>
       <c r="N16" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="O16" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A17" s="4" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="B17" s="4">
-        <v>1300000100</v>
+        <v>1300000092</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="G17" s="3">
         <v>0.05</v>
       </c>
       <c r="H17" t="s">
-        <v>120</v>
+        <v>112</v>
+      </c>
+      <c r="I17" t="s">
+        <v>113</v>
       </c>
       <c r="J17" t="s">
-        <v>121</v>
-      </c>
-      <c r="K17" t="s">
-        <v>122</v>
-      </c>
-      <c r="L17">
-        <v>42</v>
+        <v>114</v>
       </c>
       <c r="M17">
-        <v>200</v>
+        <v>4395</v>
       </c>
       <c r="N17" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="O17" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A18" s="4" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="B18" s="4">
-        <v>1300000105</v>
+        <v>1300000100</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="G18" s="3">
         <v>0.05</v>
       </c>
       <c r="H18" t="s">
+        <v>117</v>
+      </c>
+      <c r="J18" t="s">
+        <v>118</v>
+      </c>
+      <c r="K18" t="s">
+        <v>119</v>
+      </c>
+      <c r="L18">
+        <v>42</v>
+      </c>
+      <c r="M18">
+        <v>200</v>
+      </c>
+      <c r="N18" t="s">
         <v>125</v>
       </c>
-      <c r="J18" t="s">
-        <v>126</v>
-      </c>
-      <c r="K18" t="s">
+      <c r="O18" t="s">
         <v>127</v>
       </c>
-      <c r="L18">
-        <v>49</v>
-      </c>
-      <c r="M18">
-        <v>289</v>
-      </c>
-      <c r="N18" t="s">
-        <v>128</v>
-      </c>
-      <c r="O18" t="s">
-        <v>130</v>
-      </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A19" t="s">
-        <v>69</v>
-      </c>
-      <c r="B19">
-        <v>1200000058</v>
-      </c>
-      <c r="C19" t="s">
-        <v>74</v>
-      </c>
-      <c r="D19" t="s">
-        <v>12</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F19" t="s">
-        <v>71</v>
+      <c r="A19" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="B19" s="4">
+        <v>1300000105</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>84</v>
       </c>
       <c r="G19" s="3">
         <v>0.05</v>
       </c>
       <c r="H19" t="s">
-        <v>72</v>
-      </c>
-      <c r="I19" t="s">
-        <v>73</v>
+        <v>122</v>
       </c>
       <c r="J19" t="s">
-        <v>70</v>
+        <v>123</v>
       </c>
       <c r="K19" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="L19">
-        <v>118</v>
+        <v>49</v>
       </c>
       <c r="M19">
-        <v>27</v>
+        <v>289</v>
       </c>
       <c r="N19" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="O19" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="B20">
-        <v>1200000059</v>
+        <v>1200000058</v>
       </c>
       <c r="C20" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="D20" t="s">
+        <v>11</v>
+      </c>
+      <c r="E20" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E20" s="2" t="s">
-        <v>13</v>
-      </c>
       <c r="F20" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="G20" s="3">
         <v>0.05</v>
       </c>
       <c r="H20" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="I20" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="J20" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="K20" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="L20">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="M20">
         <v>27</v>
       </c>
       <c r="N20" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="O20" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="B21">
-        <v>1200000069</v>
+        <v>1200000059</v>
       </c>
       <c r="C21" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="D21" t="s">
+        <v>11</v>
+      </c>
+      <c r="E21" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E21" s="2" t="s">
-        <v>13</v>
-      </c>
       <c r="F21" t="s">
-        <v>16</v>
+        <v>68</v>
       </c>
       <c r="G21" s="3">
         <v>0.05</v>
       </c>
       <c r="H21" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="I21" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="J21" t="s">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="K21" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="L21">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="M21">
-        <v>2509</v>
+        <v>27</v>
       </c>
       <c r="N21" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="O21" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A22" s="4" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="B22" s="4">
         <v>1300000028</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="G22" s="3">
         <v>0.05</v>
       </c>
       <c r="H22" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="I22" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="J22" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="K22" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="L22">
         <v>72</v>
@@ -1907,10 +1925,10 @@
         <v>699</v>
       </c>
       <c r="N22" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="O22" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
     </row>
   </sheetData>
